--- a/uploads/sapna 30 aug.xlsx
+++ b/uploads/sapna 30 aug.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="619">
   <si>
     <t>MANNA OSWAL</t>
   </si>
@@ -1876,6 +1876,12 @@
   </si>
   <si>
     <t> </t>
+  </si>
+  <si>
+    <t>nm.ik</t>
+  </si>
+  <si>
+    <t>telugu</t>
   </si>
 </sst>
 </file>
@@ -4924,6 +4930,9 @@
       <c r="B272" s="2">
         <v>919362538652</v>
       </c>
+      <c r="C272" t="s" s="0">
+        <v>584</v>
+      </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
@@ -4932,6 +4941,9 @@
       <c r="B273" s="2">
         <v>919980411850</v>
       </c>
+      <c r="C273" t="s" s="0">
+        <v>585</v>
+      </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
@@ -4940,6 +4952,9 @@
       <c r="B274" s="2">
         <v>919886623594</v>
       </c>
+      <c r="C274" t="s" s="0">
+        <v>585</v>
+      </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
@@ -4948,6 +4963,9 @@
       <c r="B275" s="2">
         <v>919814478616</v>
       </c>
+      <c r="C275" t="s" s="0">
+        <v>585</v>
+      </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
@@ -4956,6 +4974,9 @@
       <c r="B276" s="2">
         <v>919789780262</v>
       </c>
+      <c r="C276" t="s" s="0">
+        <v>584</v>
+      </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
@@ -4964,6 +4985,9 @@
       <c r="B277" s="2">
         <v>919894600722</v>
       </c>
+      <c r="C277" t="s" s="0">
+        <v>584</v>
+      </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
@@ -4972,6 +4996,9 @@
       <c r="B278" s="2">
         <v>919444009306</v>
       </c>
+      <c r="C278" t="s" s="0">
+        <v>585</v>
+      </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
@@ -4988,6 +5015,9 @@
       <c r="B280" s="2">
         <v>919789722356</v>
       </c>
+      <c r="C280" t="s" s="0">
+        <v>618</v>
+      </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
@@ -4996,6 +5026,9 @@
       <c r="B281" s="2">
         <v>919337350844</v>
       </c>
+      <c r="C281" t="s" s="0">
+        <v>585</v>
+      </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
@@ -5003,6 +5036,9 @@
       </c>
       <c r="B282" s="2">
         <v>919022512865</v>
+      </c>
+      <c r="C282" t="s" s="0">
+        <v>584</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
